--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Informateur non professionnel du document</t>
+    <t>1.3.2- Informateur non professionnel</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Informateur non professionnel.</t>
+    <t>Informateur non professionnel ayant fourni des informations relatives au document, ou personne de confiance désignée par le patient/usager  
+ou personne à prévenir en cas d’urgence ou aidant du patient/usager ou personne aidée.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-NonProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
